--- a/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>JOHN F. KENNEDY</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.49529</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.210319</v>
-      </c>
-      <c r="I2" t="n">
-        <v>309</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.49529</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.210319</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>20396 ANTONIO ARELLANO BUITRON</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.448462</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.21646800000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>251</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.448462</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.216468</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.498951</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.204303</v>
-      </c>
-      <c r="I4" t="n">
-        <v>217</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.498951</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.204303</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>21562 OSCAR BERCKEMEYER PAZOS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.51219</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.20057199999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>304</v>
-      </c>
-      <c r="J5" t="n">
-        <v>21</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.51219</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.200572</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>CONTIGO PERU</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.533812</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.207367</v>
-      </c>
-      <c r="I6" t="n">
-        <v>221</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.533812</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.207367</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>20399 LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.444737</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.24755999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>373</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.444737</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.24756</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>400 VIRGEN DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.496513</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.214811</v>
-      </c>
-      <c r="I8" t="n">
-        <v>238</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.496513</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.214811</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>546 SAN ANTONIO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.49927</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.209839</v>
-      </c>
-      <c r="I9" t="n">
-        <v>298</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.49927</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.209839</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.500936</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.21364</v>
-      </c>
-      <c r="I10" t="n">
-        <v>305</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.500936</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.21364</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>326 SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.485187</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.207921</v>
-      </c>
-      <c r="I11" t="n">
-        <v>278</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.485187</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.207921</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>87 EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.493739</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.209289</v>
-      </c>
-      <c r="I12" t="n">
-        <v>428</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.493739</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.209289</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>21010 CLARA NICHOS MANSILLA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.495737</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.212255</v>
-      </c>
-      <c r="I13" t="n">
-        <v>738</v>
-      </c>
-      <c r="J13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.495737</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.212255</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>20403 CARLOS MARTINEZ URIBE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.495437</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.21365299999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>687</v>
-      </c>
-      <c r="J14" t="n">
-        <v>43</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.495437</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.213653</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>21559 ANTONIO GRAÑA ELIZALDE</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.485254</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.18329300000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>391</v>
-      </c>
-      <c r="J15" t="n">
-        <v>26</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.485254</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.183293</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>21009 LUIS FELIPE SUBAUSTE DEL RIO</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.494079</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.20868</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1262</v>
-      </c>
-      <c r="J16" t="n">
-        <v>55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.494079</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.20868</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>21564</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.469221</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.237201</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.469221</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.237201</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>20406</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.49727</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.20399999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>417</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.49727</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.204</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>20845 MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.498396</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.230907</v>
-      </c>
-      <c r="I19" t="n">
-        <v>361</v>
-      </c>
-      <c r="J19" t="n">
-        <v>19</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.498396</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.230907</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>20407</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.485843</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.205146</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1578</v>
-      </c>
-      <c r="J20" t="n">
-        <v>86</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.485843</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.205146</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1578</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>20826 SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.501272</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.21366</v>
-      </c>
-      <c r="I21" t="n">
-        <v>598</v>
-      </c>
-      <c r="J21" t="n">
-        <v>33</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.501272</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.21366</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.495857</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.209667</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J22" t="n">
-        <v>85</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.495857</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.209667</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.473603</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.226164</v>
-      </c>
-      <c r="I23" t="n">
-        <v>701</v>
-      </c>
-      <c r="J23" t="n">
-        <v>40</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.473603</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.226164</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SANTA INES SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.502082</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.208619</v>
-      </c>
-      <c r="I24" t="n">
-        <v>582</v>
-      </c>
-      <c r="J24" t="n">
-        <v>37</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.502082</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.208619</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.496153</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.212334</v>
-      </c>
-      <c r="I25" t="n">
-        <v>883</v>
-      </c>
-      <c r="J25" t="n">
-        <v>43</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.496153</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.212334</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>INKA GAKUEN</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.49838</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.210075</v>
-      </c>
-      <c r="I26" t="n">
-        <v>437</v>
-      </c>
-      <c r="J26" t="n">
-        <v>36</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.49838</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.210075</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>HOGAR INFANTIL</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.492923</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.207415</v>
-      </c>
-      <c r="I27" t="n">
-        <v>295</v>
-      </c>
-      <c r="J27" t="n">
-        <v>31</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.492923</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.207415</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>MARIA MONTESSORI</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.496001</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.21519499999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>252</v>
-      </c>
-      <c r="J28" t="n">
-        <v>21</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.496001</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.215195</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>EL NAZARENO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.495885</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.21445799999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>346</v>
-      </c>
-      <c r="J29" t="n">
-        <v>30</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.495885</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.214458</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>PLAY SCHOOL</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.492895</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.213442</v>
-      </c>
-      <c r="I30" t="n">
-        <v>427</v>
-      </c>
-      <c r="J30" t="n">
-        <v>46</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.492895</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.213442</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>20388 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.607766</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.2179</v>
-      </c>
-      <c r="I31" t="n">
-        <v>787</v>
-      </c>
-      <c r="J31" t="n">
-        <v>43</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.607766</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.2179</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SAN JOSE</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.544527</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.182968</v>
-      </c>
-      <c r="I32" t="n">
-        <v>25</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.544527</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.182968</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>21551 CAPITAN JUAN VICENTE SUAREZ</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.503838</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.154065</v>
-      </c>
-      <c r="I33" t="n">
-        <v>233</v>
-      </c>
-      <c r="J33" t="n">
-        <v>17</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.503838</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.154065</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>20386 JORGE BASADRE</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.557311</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.17938700000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>646</v>
-      </c>
-      <c r="J34" t="n">
-        <v>50</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.557311</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.179387</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>CRISTO REDENTOR</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.496597</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.20569500000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>251</v>
-      </c>
-      <c r="J35" t="n">
-        <v>29</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.496597</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.205695</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>JEDCER</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.499952</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.226311</v>
-      </c>
-      <c r="I36" t="n">
-        <v>294</v>
-      </c>
-      <c r="J36" t="n">
-        <v>31</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.499952</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.226311</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>ISAAC NEWTON</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.491373</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.206973</v>
-      </c>
-      <c r="I37" t="n">
-        <v>392</v>
-      </c>
-      <c r="J37" t="n">
-        <v>32</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.491373</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.206973</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>BEN CARSON</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-11.497494</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.20938700000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-11.497494</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.209387</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.495363</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.211125</v>
-      </c>
-      <c r="I39" t="n">
-        <v>443</v>
-      </c>
-      <c r="J39" t="n">
-        <v>31</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.495363</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.211125</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>20902 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.450185</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.26794099999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>265</v>
-      </c>
-      <c r="J40" t="n">
-        <v>19</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.450185</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.267941</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>21570 ESTRELLITA DE BELEN</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.52266</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.28343</v>
-      </c>
-      <c r="I41" t="n">
-        <v>219</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.52266</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.28343</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SALESIANO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.499675</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.20825499999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>169</v>
-      </c>
-      <c r="J42" t="n">
-        <v>22</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.499675</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.208255</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>INGENIEROS UNI DE HUARAL</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.490401</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.207989</v>
-      </c>
-      <c r="I43" t="n">
-        <v>297</v>
-      </c>
-      <c r="J43" t="n">
-        <v>32</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.490401</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.207989</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>PROLOG DE HUARAL</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.489495</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.206895</v>
-      </c>
-      <c r="I44" t="n">
-        <v>273</v>
-      </c>
-      <c r="J44" t="n">
-        <v>18</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.489495</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.206895</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>219206</t>
+          <t>354925</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JOHN F. KENNEDY</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.49529</t>
+          <t>-11.469221</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.210319</t>
+          <t>-77.237201</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>354586</t>
+          <t>354690</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20396 ANTONIO ARELLANO BUITRON</t>
+          <t>400 VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.448462</t>
+          <t>-11.496513</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.216468</t>
+          <t>-77.214811</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>354591</t>
+          <t>354614</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
+          <t>CONTIGO PERU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.498951</t>
+          <t>-11.533812</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.204303</t>
+          <t>-77.207367</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>354609</t>
+          <t>354713</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21562 OSCAR BERCKEMEYER PAZOS</t>
+          <t>546 SAN ANTONIO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.51219</t>
+          <t>-11.49927</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.200572</t>
+          <t>-77.209839</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>354614</t>
+          <t>354732</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CONTIGO PERU</t>
+          <t>326 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.533812</t>
+          <t>-11.485187</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.207367</t>
+          <t>-77.207921</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>354671</t>
+          <t>354727</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20399 LA ESPERANZA</t>
+          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.444737</t>
+          <t>-11.500936</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.24756</t>
+          <t>-77.21364</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>354690</t>
+          <t>355675</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>400 VIRGEN DEL ROSARIO</t>
+          <t>21551 CAPITAN JUAN VICENTE SUAREZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.496513</t>
+          <t>-11.503838</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.214811</t>
+          <t>-77.154065</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>354713</t>
+          <t>838551</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>546 SAN ANTONIO</t>
+          <t>PROLOG DE HUARAL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.49927</t>
+          <t>-11.489495</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.209839</t>
+          <t>-77.206895</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>354727</t>
+          <t>354586</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>20396 ANTONIO ARELLANO BUITRON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.500936</t>
+          <t>-11.448462</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.21364</t>
+          <t>-77.216468</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>354732</t>
+          <t>354746</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>326 SAN JUAN BAUTISTA</t>
+          <t>87 EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.485187</t>
+          <t>-11.493739</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.207921</t>
+          <t>-77.209289</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>354746</t>
+          <t>354987</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87 EMILIA BARCIA BONIFFATTI</t>
+          <t>20845 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.493739</t>
+          <t>-11.498396</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.209289</t>
+          <t>-77.230907</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>734153</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21010 CLARA NICHOS MANSILLA</t>
+          <t>20902 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.495737</t>
+          <t>-11.450185</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.212255</t>
+          <t>-77.267941</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>354794</t>
+          <t>355637</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20403 CARLOS MARTINEZ URIBE</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.495437</t>
+          <t>-11.544527</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.213653</t>
+          <t>-77.182968</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>354869</t>
+          <t>629393</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21559 ANTONIO GRAÑA ELIZALDE</t>
+          <t>BEN CARSON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.485254</t>
+          <t>-11.497494</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.183293</t>
+          <t>-77.209387</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>354874</t>
+          <t>354609</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21009 LUIS FELIPE SUBAUSTE DEL RIO</t>
+          <t>21562 OSCAR BERCKEMEYER PAZOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.494079</t>
+          <t>-11.51219</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.20868</t>
+          <t>-77.200572</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>354925</t>
+          <t>355246</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.469221</t>
+          <t>-11.496001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.237201</t>
+          <t>-77.215195</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>354968</t>
+          <t>354671</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>20399 LA ESPERANZA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.49727</t>
+          <t>-11.444737</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.204</t>
+          <t>-77.24756</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>354987</t>
+          <t>354968</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20845 MARIANO MELGAR</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.498396</t>
+          <t>-11.49727</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.230907</t>
+          <t>-77.204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>354992</t>
+          <t>734313</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>SALESIANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.485843</t>
+          <t>-11.499675</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.205146</t>
+          <t>-77.208255</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>169</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>219206</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20826 SAN JUAN BAUTISTA</t>
+          <t>JOHN F. KENNEDY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.501272</t>
+          <t>-11.49529</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.21366</t>
+          <t>-77.210319</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>355010</t>
+          <t>354869</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>21559 ANTONIO GRAÑA ELIZALDE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.495857</t>
+          <t>-11.485254</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.209667</t>
+          <t>-77.183293</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>391</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>504294</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.473603</t>
+          <t>-11.496597</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.226164</t>
+          <t>-77.205695</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>355091</t>
+          <t>355307</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANTA INES SACO OLIVEROS</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.502082</t>
+          <t>-11.495885</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.208619</t>
+          <t>-77.214458</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>355109</t>
+          <t>355166</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>HOGAR INFANTIL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.496153</t>
+          <t>-11.492923</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.212334</t>
+          <t>-77.207415</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>355152</t>
+          <t>592808</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>INKA GAKUEN</t>
+          <t>JEDCER</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.49838</t>
+          <t>-11.499952</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.210075</t>
+          <t>-77.226311</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,27 +2051,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>355166</t>
+          <t>734129</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HOGAR INFANTIL</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.492923</t>
+          <t>-11.495363</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.207415</t>
+          <t>-77.211125</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>355246</t>
+          <t>354770</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARIA MONTESSORI</t>
+          <t>21010 CLARA NICHOS MANSILLA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.496001</t>
+          <t>-11.495737</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.215195</t>
+          <t>-77.212255</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>738</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>355307</t>
+          <t>596284</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.495885</t>
+          <t>-11.491373</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.214458</t>
+          <t>-77.206973</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>355374</t>
+          <t>802123</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PLAY SCHOOL</t>
+          <t>INGENIEROS UNI DE HUARAL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.492895</t>
+          <t>-11.490401</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.213442</t>
+          <t>-77.207989</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>297</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>355623</t>
+          <t>355005</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20388 JOSE CARLOS MARIATEGUI</t>
+          <t>20826 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.607766</t>
+          <t>-11.501272</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.2179</t>
+          <t>-77.21366</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>598</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>355637</t>
+          <t>355152</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>INKA GAKUEN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.544527</t>
+          <t>-11.49838</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.182968</t>
+          <t>-77.210075</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>437</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>355675</t>
+          <t>355091</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>21551 CAPITAN JUAN VICENTE SUAREZ</t>
+          <t>SANTA INES SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.503838</t>
+          <t>-11.502082</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.154065</t>
+          <t>-77.208619</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>582</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>355722</t>
+          <t>355067</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20386 JORGE BASADRE</t>
+          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.557311</t>
+          <t>-11.473603</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.179387</t>
+          <t>-77.226164</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>701</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>504294</t>
+          <t>354794</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>20403 CARLOS MARTINEZ URIBE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.496597</t>
+          <t>-11.495437</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.205695</t>
+          <t>-77.213653</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>687</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>592808</t>
+          <t>355109</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JEDCER</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.499952</t>
+          <t>-11.496153</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.226311</t>
+          <t>-77.212334</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>883</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>596284</t>
+          <t>355623</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>20388 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.491373</t>
+          <t>-11.607766</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.206973</t>
+          <t>-77.2179</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>787</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>629393</t>
+          <t>355374</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BEN CARSON</t>
+          <t>PLAY SCHOOL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.497494</t>
+          <t>-11.492895</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.209387</t>
+          <t>-77.213442</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>427</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>734129</t>
+          <t>355722</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>20386 JORGE BASADRE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.495363</t>
+          <t>-11.557311</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.211125</t>
+          <t>-77.179387</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>646</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>734153</t>
+          <t>354874</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20902 TUPAC AMARU</t>
+          <t>21009 LUIS FELIPE SUBAUSTE DEL RIO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.450185</t>
+          <t>-11.494079</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.267941</t>
+          <t>-77.20868</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>734252</t>
+          <t>354591</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21570 ESTRELLITA DE BELEN</t>
+          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.52266</t>
+          <t>-11.498951</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.28343</t>
+          <t>-77.204303</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>734313</t>
+          <t>355010</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SALESIANO</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.499675</t>
+          <t>-11.495857</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.208255</t>
+          <t>-77.209667</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>802123</t>
+          <t>354992</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>INGENIEROS UNI DE HUARAL</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.490401</t>
+          <t>-11.485843</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.207989</t>
+          <t>-77.205146</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>838551</t>
+          <t>734252</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PROLOG DE HUARAL</t>
+          <t>21570 ESTRELLITA DE BELEN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.489495</t>
+          <t>-11.52266</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.206895</t>
+          <t>-77.28343</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>354925</t>
+          <t>838551</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>PROLOG DE HUARAL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.469221</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.237201</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-11.489495</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-77.206895</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>354690</t>
+          <t>802123</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>400 VIRGEN DEL ROSARIO</t>
+          <t>INGENIEROS UNI DE HUARAL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.496513</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.214811</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.490401</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.207989</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>354614</t>
+          <t>734313</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CONTIGO PERU</t>
+          <t>SALESIANO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.533812</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.207367</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-11.499675</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.208255</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>354713</t>
+          <t>734252</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>546 SAN ANTONIO</t>
+          <t>21570 ESTRELLITA DE BELEN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.49927</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.209839</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-11.52266</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.28343</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>354732</t>
+          <t>734153</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>326 SAN JUAN BAUTISTA</t>
+          <t>20902 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.485187</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.207921</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-11.450185</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.267941</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>354727</t>
+          <t>734129</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.500936</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.21364</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-11.495363</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.211125</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>355675</t>
+          <t>629393</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21551 CAPITAN JUAN VICENTE SUAREZ</t>
+          <t>BEN CARSON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.503838</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.154065</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-11.497494</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.209387</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>838551</t>
+          <t>596284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PROLOG DE HUARAL</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.489495</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.206895</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>-11.491373</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.206973</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>354586</t>
+          <t>592808</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20396 ANTONIO ARELLANO BUITRON</t>
+          <t>JEDCER</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.448462</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.216468</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-11.499952</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.226311</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>354746</t>
+          <t>504294</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>87 EMILIA BARCIA BONIFFATTI</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.493739</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.209289</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-11.496597</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.205695</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>354987</t>
+          <t>355722</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20845 MARIANO MELGAR</t>
+          <t>20386 JORGE BASADRE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.498396</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.230907</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>-11.557311</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.179387</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>734153</t>
+          <t>355675</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20902 TUPAC AMARU</t>
+          <t>21551 CAPITAN JUAN VICENTE SUAREZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.450185</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.267941</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-11.503838</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.154065</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-11.544527</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-77.182968</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>629393</t>
+          <t>355623</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BEN CARSON</t>
+          <t>20388 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.497494</t>
+          <t>787</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.209387</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-11.607766</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.2179</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>354609</t>
+          <t>355374</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21562 OSCAR BERCKEMEYER PAZOS</t>
+          <t>PLAY SCHOOL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.51219</t>
+          <t>427</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.200572</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-11.492895</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.213442</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>355246</t>
+          <t>355307</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MARIA MONTESSORI</t>
+          <t>EL NAZARENO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.496001</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.215195</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-11.495885</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.214458</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>354671</t>
+          <t>355246</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20399 LA ESPERANZA</t>
+          <t>MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.444737</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.24756</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>-11.496001</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.215195</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>354968</t>
+          <t>355166</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>HOGAR INFANTIL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.49727</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.204</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-11.492923</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.207415</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>734313</t>
+          <t>355152</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SALESIANO</t>
+          <t>INKA GAKUEN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.499675</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.208255</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>-11.49838</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.210075</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>219206</t>
+          <t>355109</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JOHN F. KENNEDY</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.49529</t>
+          <t>883</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.210319</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>-11.496153</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.212334</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>354869</t>
+          <t>355091</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21559 ANTONIO GRAÑA ELIZALDE</t>
+          <t>SANTA INES SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.485254</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.183293</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>-11.5019917</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.20876512</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>504294</t>
+          <t>355067</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.496597</t>
+          <t>701</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.205695</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-11.473603</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.226164</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>355307</t>
+          <t>355010</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EL NAZARENO</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.495885</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.214458</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-11.495857</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.209667</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>355166</t>
+          <t>355005</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HOGAR INFANTIL</t>
+          <t>20826 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.492923</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.207415</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-11.501272</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.21366</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>592808</t>
+          <t>354992</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JEDCER</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.499952</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.226311</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-11.485843</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.205146</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>734129</t>
+          <t>354987</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>20845 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.495363</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.211125</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-11.498396</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.230907</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>354968</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21010 CLARA NICHOS MANSILLA</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.495737</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.212255</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>-11.49727</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.204</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>596284</t>
+          <t>354925</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.491373</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.206973</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-11.469221</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.237201</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>802123</t>
+          <t>354874</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INGENIEROS UNI DE HUARAL</t>
+          <t>21009 LUIS FELIPE SUBAUSTE DEL RIO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.490401</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.207989</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>-11.494079</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.20868</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>354869</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20826 SAN JUAN BAUTISTA</t>
+          <t>21559 ANTONIO GRAÑA ELIZALDE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.501272</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.21366</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>-11.485254</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.183293</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>355152</t>
+          <t>354794</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INKA GAKUEN</t>
+          <t>20403 CARLOS MARTINEZ URIBE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.49838</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.210075</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>-11.495437</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.213653</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>355091</t>
+          <t>354770</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SANTA INES SACO OLIVEROS</t>
+          <t>21010 CLARA NICHOS MANSILLA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.502082</t>
+          <t>738</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.208619</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>-11.495737</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.212255</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>354746</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
+          <t>87 EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.473603</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.226164</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>-11.493739</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.209289</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>354794</t>
+          <t>354732</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20403 CARLOS MARTINEZ URIBE</t>
+          <t>326 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.495437</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.213653</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>-11.485187</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.207921</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>355109</t>
+          <t>354727</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.496153</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.212334</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>-11.500936</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.21364</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>355623</t>
+          <t>354713</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20388 JOSE CARLOS MARIATEGUI</t>
+          <t>546 SAN ANTONIO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.607766</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.2179</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>-11.49927</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.209839</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>355374</t>
+          <t>354690</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PLAY SCHOOL</t>
+          <t>400 VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.492895</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.213442</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>-11.496513</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.214811</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>355722</t>
+          <t>354671</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20386 JORGE BASADRE</t>
+          <t>20399 LA ESPERANZA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.557311</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.179387</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>-11.444737</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.24756</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>354874</t>
+          <t>354614</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21009 LUIS FELIPE SUBAUSTE DEL RIO</t>
+          <t>CONTIGO PERU</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.494079</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.20868</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>-11.533812</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.207367</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>354591</t>
+          <t>354609</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
+          <t>21562 OSCAR BERCKEMEYER PAZOS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.498951</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.204303</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-11.51219</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-77.200572</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>355010</t>
+          <t>354591</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.495857</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.209667</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>-11.498951</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-77.204303</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>354992</t>
+          <t>354586</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20396 ANTONIO ARELLANO BUITRON</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.485843</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.205146</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>-11.448462</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-77.216468</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>734252</t>
+          <t>219206</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21570 ESTRELLITA DE BELEN</t>
+          <t>JOHN F. KENNEDY</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.52266</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.28343</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-11.49529</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.210319</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
+++ b/ZonasEscolares/excels/LIMA-HUARAL-HUARAL.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
